--- a/measurements/35/Filled_2D_sections/axial/week35_axial_Batch_Allmarks.xlsx
+++ b/measurements/35/Filled_2D_sections/axial/week35_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +616,79 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11.80249851279001</v>
+        <v>4498.866213151927</v>
       </c>
       <c r="D2" t="n">
-        <v>31.81800553275318</v>
+        <v>621.2086794489906</v>
       </c>
       <c r="E2" t="n">
-        <v>15.35394522329656</v>
+        <v>299.7675019786471</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0723016182496</v>
+        <v>2.072301618249599</v>
       </c>
       <c r="G2" t="n">
         <v>0.1465000970392067</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6286204268292683</v>
+        <v>3.597470238095238</v>
       </c>
       <c r="J2" t="n">
-        <v>1.956364329268293</v>
+        <v>38.19568452380952</v>
       </c>
       <c r="K2" t="n">
-        <v>1.200219131097561</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>12.4077380952381</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>38.19568452380952</v>
+      </c>
+      <c r="N2" t="n">
+        <v>29.98325892857143</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>4.713541666666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>13.27938988095238</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.899553571428571</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.008556547619047</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.794642857142857</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.597470238095238</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>11.70080309339679</v>
+      <c r="AK2" s="2" t="n">
+        <v>4460.102040816326</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +699,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.81142177275431</v>
+        <v>4502.267573696145</v>
       </c>
       <c r="D3" t="n">
-        <v>32.82912366564681</v>
+        <v>640.9495572816758</v>
       </c>
       <c r="E3" t="n">
-        <v>15.48845057080432</v>
+        <v>302.3935587633223</v>
       </c>
       <c r="F3" t="n">
         <v>2.119587334806079</v>
@@ -572,24 +718,60 @@
         <v>0.1377188736637995</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6319550304878049</v>
+        <v>2.183779761904762</v>
       </c>
       <c r="J3" t="n">
-        <v>1.979325457317073</v>
+        <v>38.64397321428572</v>
       </c>
       <c r="K3" t="n">
-        <v>1.216010861280488</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>13.05691964285714</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>38.64397321428572</v>
+      </c>
+      <c r="N3" t="n">
+        <v>29.98325892857143</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13.99925595238095</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.902901785714286</v>
+      </c>
+      <c r="X3" t="n">
+        <v>12.33816964285714</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.397693452380953</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.770461309523809</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.183779761904762</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>29.49325117119929</v>
+      <c r="AK3" s="2" t="n">
+        <v>575.820618104367</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +782,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.92236763831053</v>
+        <v>4544.557823129251</v>
       </c>
       <c r="D4" t="n">
-        <v>30.76749166046701</v>
+        <v>600.6986467043558</v>
       </c>
       <c r="E4" t="n">
-        <v>15.71214746556631</v>
+        <v>306.7609743277231</v>
       </c>
       <c r="F4" t="n">
         <v>1.958197740181282</v>
@@ -619,24 +801,63 @@
         <v>0.1582662056593236</v>
       </c>
       <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.828497023809524</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40.00186011904761</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10.03890749007936</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>40.00186011904761</v>
+      </c>
+      <c r="N4" t="n">
+        <v>18.30171130952381</v>
+      </c>
+      <c r="O4" t="n">
+        <v>14.97023809523809</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5.256696428571428</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11.40997023809524</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.707589285714286</v>
+      </c>
+      <c r="Z4" t="n">
         <v>4</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.5844131097560976</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.048875762195122</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.084365472560976</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="AD4" t="n">
+        <v>1.828497023809524</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.899925595238095</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.163783482142857</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>15.23691411381815</v>
+      <c r="AK4" s="2" t="n">
+        <v>297.4826088888304</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +868,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.89678762641285</v>
+        <v>4534.807256235827</v>
       </c>
       <c r="D5" t="n">
-        <v>30.99321927675387</v>
+        <v>605.105709689004</v>
       </c>
       <c r="E5" t="n">
-        <v>15.89644863547348</v>
+        <v>310.3592352640061</v>
       </c>
       <c r="F5" t="n">
         <v>1.9496945504917</v>
@@ -666,23 +887,62 @@
         <v>0.1556346148007862</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5816501524390244</v>
+        <v>1.575520833333333</v>
       </c>
       <c r="J5" t="n">
-        <v>2.066120426829269</v>
+        <v>40.33854166666666</v>
       </c>
       <c r="K5" t="n">
-        <v>1.083817644817073</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>9.763299851190474</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40.33854166666666</v>
+      </c>
+      <c r="N5" t="n">
+        <v>17.56696428571428</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15.37946428571428</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11.35602678571428</v>
+      </c>
+      <c r="U5" t="n">
+        <v>8.876488095238095</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.592261904761904</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.575520833333333</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>4.35453869047619</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.841641865079364</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.934763146939909</v>
       </c>
     </row>
@@ -694,17 +954,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.88935157644259</v>
+        <v>4531.972789115646</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02843031069128</v>
+        <v>586.2693536849249</v>
       </c>
       <c r="E6" t="n">
-        <v>15.90828480662369</v>
+        <v>310.5903224150339</v>
       </c>
       <c r="F6" t="n">
         <v>1.887596977028499</v>
@@ -713,23 +973,62 @@
         <v>0.1656924700483306</v>
       </c>
       <c r="H6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.515997023809524</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.24553571428572</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9.200005723443223</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>40.24553571428572</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17.53348214285714</v>
+      </c>
+      <c r="O6" t="n">
+        <v>14.76190476190476</v>
+      </c>
+      <c r="S6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.6304306402439025</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.061356707317073</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.086485327743903</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="W6" t="n">
+        <v>6.080729166666666</v>
+      </c>
+      <c r="X6" t="n">
+        <v>12.30840773809524</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8.353794642857142</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.515997023809524</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.082217261904762</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.273995535714286</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AK6" s="2" t="n">
         <v>0.1716428418731661</v>
       </c>
     </row>
@@ -741,43 +1040,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11.72397382510411</v>
+        <v>4468.934240362812</v>
       </c>
       <c r="D7" t="n">
-        <v>29.62778623220397</v>
+        <v>578.4472550096966</v>
       </c>
       <c r="E7" t="n">
-        <v>15.68949058579236</v>
+        <v>306.3186257226126</v>
       </c>
       <c r="F7" t="n">
         <v>1.888384206625132</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1678364554963936</v>
+        <v>0.1678364554963935</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6125190548780488</v>
+        <v>1.489955357142857</v>
       </c>
       <c r="J7" t="n">
-        <v>2.02953506097561</v>
+        <v>39.62425595238095</v>
       </c>
       <c r="K7" t="n">
-        <v>1.064453125</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>8.345362103174603</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>39.62425595238095</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14.04575892857143</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5.119047619047619</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11.95870535714286</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.390997023809523</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.489955357142857</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3.692336309523809</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.436490221088435</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>3.6</v>
+      <c r="AK7" s="2" t="n">
+        <v>14.15</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1126,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11.76412849494349</v>
+        <v>4484.240362811791</v>
       </c>
       <c r="D8" t="n">
-        <v>29.58492384596569</v>
+        <v>577.6104179450443</v>
       </c>
       <c r="E8" t="n">
-        <v>15.55151851584272</v>
+        <v>303.6248853093102</v>
       </c>
       <c r="F8" t="n">
         <v>1.90238167519312</v>
@@ -807,24 +1145,60 @@
         <v>0.1688996354122387</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.578125</v>
+        <v>1.380208333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>2.000571646341463</v>
+        <v>39.05877976190476</v>
       </c>
       <c r="K8" t="n">
-        <v>1.032178925304878</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>8.038105867346939</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>39.05877976190476</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17.44605654761905</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>12.81622023809524</v>
+      </c>
+      <c r="U8" t="n">
+        <v>11.28720238095238</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.889136904761904</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.380208333333333</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4.47172619047619</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.892898478835979</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.7688786204268293</v>
+      <c r="AK8" s="2" t="n">
+        <v>1.764415922619047</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1209,79 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11.84562760261749</v>
+        <v>4515.306122448979</v>
       </c>
       <c r="D9" t="n">
-        <v>31.74513213808944</v>
+        <v>619.7859131722223</v>
       </c>
       <c r="E9" t="n">
-        <v>15.30169801014226</v>
+        <v>298.7474373408726</v>
       </c>
       <c r="F9" t="n">
-        <v>2.074614994822677</v>
+        <v>2.074614994822676</v>
       </c>
       <c r="G9" t="n">
         <v>0.1477112798404513</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5827934451219512</v>
+        <v>1.592261904761905</v>
       </c>
       <c r="J9" t="n">
-        <v>1.987042682926829</v>
+        <v>38.79464285714285</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9511623475609756</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>8.559771825396821</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>38.79464285714285</v>
+      </c>
+      <c r="N9" t="n">
+        <v>17.60788690476191</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.605654761904762</v>
+      </c>
+      <c r="X9" t="n">
+        <v>13.06175595238095</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.614831349206348</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.592261904761905</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.900722789115646</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.804201600609756</v>
+      <c r="AK9" s="2" t="n">
+        <v>35.22488839285714</v>
       </c>
     </row>
     <row r="10">
@@ -882,43 +1292,82 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.58120166567519</v>
+        <v>4414.512471655328</v>
       </c>
       <c r="D10" t="n">
-        <v>33.57123110061739</v>
+        <v>655.4383214882441</v>
       </c>
       <c r="E10" t="n">
-        <v>15.67275174361903</v>
+        <v>305.9918197563716</v>
       </c>
       <c r="F10" t="n">
-        <v>2.142012561022381</v>
+        <v>2.14201256102238</v>
       </c>
       <c r="G10" t="n">
         <v>0.1291305357244266</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6420541158536586</v>
+        <v>1.50297619047619</v>
       </c>
       <c r="J10" t="n">
-        <v>1.911585365853659</v>
+        <v>37.32142857142857</v>
       </c>
       <c r="K10" t="n">
-        <v>1.043978658536586</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>9.677003613945576</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>15.2250744047619</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>37.32142857142857</v>
+      </c>
+      <c r="R10" t="n">
+        <v>22.3442150297619</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12.53534226190476</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5.870535714285714</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.914434523809524</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.50297619047619</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3.254411139455782</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.15775771722561</v>
+      <c r="AK10" s="2" t="n">
+        <v>8.931879933213269</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1378,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11.72040452111838</v>
+        <v>4467.573696145125</v>
       </c>
       <c r="D11" t="n">
-        <v>29.92740260100946</v>
+        <v>584.2969079244704</v>
       </c>
       <c r="E11" t="n">
-        <v>16.06054429600879</v>
+        <v>313.563007683981</v>
       </c>
       <c r="F11" t="n">
         <v>1.863411479052222</v>
@@ -948,16 +1397,63 @@
         <v>0.1644426296877362</v>
       </c>
       <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.579241071428571</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.3359375</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.077380952380953</v>
+      </c>
+      <c r="L11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.7004573170731707</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.758669969512195</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.100538300304878</v>
+      <c r="P11" t="n">
+        <v>13.67559523809524</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>34.3359375</v>
+      </c>
+      <c r="R11" t="n">
+        <v>21.48670014880953</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>4.674479166666666</v>
+      </c>
+      <c r="X11" t="n">
+        <v>7.777157738095237</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.150018601190476</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.579241071428571</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.337797619047619</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.756076388888889</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1464,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11.64306960142772</v>
+        <v>4438.095238095238</v>
       </c>
       <c r="D12" t="n">
-        <v>31.36570899660995</v>
+        <v>612.3781280290513</v>
       </c>
       <c r="E12" t="n">
-        <v>15.16127460758861</v>
+        <v>296.0058375767299</v>
       </c>
       <c r="F12" t="n">
         <v>2.068804227113636</v>
@@ -987,16 +1483,63 @@
         <v>0.1487192340255303</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6663490853658537</v>
+        <v>1.404389880952381</v>
       </c>
       <c r="J12" t="n">
-        <v>1.516863567073171</v>
+        <v>29.61495535714285</v>
       </c>
       <c r="K12" t="n">
-        <v>1.045731707317073</v>
+        <v>8.127790178571429</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>29.61495535714285</v>
+      </c>
+      <c r="N12" t="n">
+        <v>20.47247023809524</v>
+      </c>
+      <c r="O12" t="n">
+        <v>18.56956845238095</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" t="n">
+        <v>4.611235119047619</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.00967261904762</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6.874468537414965</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.404389880952381</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4.367559523809524</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.211061507936507</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>35.15780009920635</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1550,82 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12.09488399762046</v>
+        <v>4610.31746031746</v>
       </c>
       <c r="D13" t="n">
-        <v>28.93403864488369</v>
+        <v>564.9026592572529</v>
       </c>
       <c r="E13" t="n">
-        <v>14.88879719303876</v>
+        <v>290.6860404355185</v>
       </c>
       <c r="F13" t="n">
         <v>1.943342922181234</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1815488310965534</v>
+        <v>0.1815488310965535</v>
       </c>
       <c r="H13" t="n">
+        <v>17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.599702380952381</v>
+      </c>
+      <c r="J13" t="n">
+        <v>29.17224702380952</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.119660364145658</v>
+      </c>
+      <c r="L13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.7519054878048781</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.494188262195122</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.070884146341464</v>
+      <c r="M13" t="n">
+        <v>29.17224702380952</v>
+      </c>
+      <c r="N13" t="n">
+        <v>18.87090773809524</v>
+      </c>
+      <c r="O13" t="n">
+        <v>14.68005952380952</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5.786830357142857</v>
+      </c>
+      <c r="X13" t="n">
+        <v>7.894345238095237</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.550719246031744</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.599702380952381</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.118303571428571</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.375837053571428</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>21.33091517857143</v>
       </c>
     </row>
     <row r="14">
@@ -1046,35 +1636,82 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.05145746579417</v>
+        <v>4593.764172335601</v>
       </c>
       <c r="D14" t="n">
-        <v>28.45460317483763</v>
+        <v>555.5422524611155</v>
       </c>
       <c r="E14" t="n">
-        <v>14.702044719603</v>
+        <v>287.0399207160586</v>
       </c>
       <c r="F14" t="n">
         <v>1.935418080785567</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1870442533139597</v>
+        <v>0.1870442533139598</v>
       </c>
       <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29.41964285714285</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.269424957482993</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>29.41964285714285</v>
+      </c>
+      <c r="N14" t="n">
+        <v>19.73586309523809</v>
+      </c>
+      <c r="O14" t="n">
+        <v>14.18526785714286</v>
+      </c>
+      <c r="S14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.577172256097561</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.506859756097561</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.9553639481707317</v>
+      <c r="W14" t="n">
+        <v>5.853794642857142</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11.26860119047619</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.812499999999999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.220610119047619</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.025882227891156</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>15.83224826388889</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1722,82 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11.94527067221892</v>
+        <v>4553.28798185941</v>
       </c>
       <c r="D15" t="n">
-        <v>29.131611981043</v>
+        <v>568.760043439411</v>
       </c>
       <c r="E15" t="n">
-        <v>14.93165965778072</v>
+        <v>291.5228790328616</v>
       </c>
       <c r="F15" t="n">
         <v>1.950996248823744</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1768792245494358</v>
+        <v>0.1768792245494357</v>
       </c>
       <c r="H15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="J15" t="n">
+        <v>29.56845238095238</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8.554953231292515</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>29.56845238095238</v>
+      </c>
+      <c r="N15" t="n">
+        <v>19.99255952380952</v>
+      </c>
+      <c r="O15" t="n">
+        <v>14.7953869047619</v>
+      </c>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.5761242378048781</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.514481707317073</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.9681068978658538</v>
+      <c r="W15" t="n">
+        <v>6.023065476190476</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.24813988095238</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.081752232142858</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.616443452380952</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>4.410342261904762</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3.297991071428572</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>14.45033482142857</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1808,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11.71624033313504</v>
+        <v>4465.986394557823</v>
       </c>
       <c r="D16" t="n">
-        <v>28.37623235655994</v>
+        <v>554.0121555328369</v>
       </c>
       <c r="E16" t="n">
-        <v>15.08391918496388</v>
+        <v>294.495565039771</v>
       </c>
       <c r="F16" t="n">
         <v>1.881224104200071</v>
@@ -1143,16 +1827,63 @@
         <v>0.1828473507968046</v>
       </c>
       <c r="H16" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.408854166666667</v>
+      </c>
+      <c r="J16" t="n">
+        <v>30.62127976190476</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.561596513605441</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.9232088414634146</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.568407012195122</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.18286331300813</v>
+      <c r="M16" t="n">
+        <v>30.62127976190476</v>
+      </c>
+      <c r="N16" t="n">
+        <v>20.63616071428571</v>
+      </c>
+      <c r="O16" t="n">
+        <v>18.02455357142857</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.469866071428571</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8.020833333333332</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6.792689732142856</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.408854166666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>4.157366071428571</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3.34422831632653</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>35.82868303571428</v>
       </c>
     </row>
     <row r="17">
@@ -1163,35 +1894,82 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.46192742415229</v>
+        <v>4369.047619047618</v>
       </c>
       <c r="D17" t="n">
-        <v>27.68882347897786</v>
+        <v>540.5913155419486</v>
       </c>
       <c r="E17" t="n">
-        <v>15.74173777277877</v>
+        <v>307.3386898494902</v>
       </c>
       <c r="F17" t="n">
         <v>1.75894325509973</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1878704661811202</v>
+        <v>0.1878704661811201</v>
       </c>
       <c r="H17" t="n">
+        <v>16</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32.08891369047619</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7.754836309523811</v>
+      </c>
+      <c r="L17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.9442644817073171</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.643578506097561</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.227388211382114</v>
+      <c r="M17" t="n">
+        <v>32.08891369047619</v>
+      </c>
+      <c r="N17" t="n">
+        <v>21.36532738095238</v>
+      </c>
+      <c r="O17" t="n">
+        <v>18.43563988095238</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.575892857142857</v>
+      </c>
+      <c r="X17" t="n">
+        <v>9.014136904761905</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.787946428571429</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3.776041666666667</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.905970982142856</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>21.91545758928572</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1980,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11.4622248661511</v>
+        <v>4369.160997732426</v>
       </c>
       <c r="D18" t="n">
-        <v>26.85017041752978</v>
+        <v>524.2176129136766</v>
       </c>
       <c r="E18" t="n">
-        <v>14.96961939625624</v>
+        <v>292.2639977364313</v>
       </c>
       <c r="F18" t="n">
         <v>1.793644160668825</v>
@@ -1221,16 +1999,63 @@
         <v>0.1997950366631805</v>
       </c>
       <c r="H18" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.15476190476191</v>
+      </c>
+      <c r="K18" t="n">
+        <v>8.002728174603174</v>
+      </c>
+      <c r="L18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.9291158536585367</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.698170731707317</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.252381859756098</v>
+      <c r="M18" t="n">
+        <v>33.15476190476191</v>
+      </c>
+      <c r="N18" t="n">
+        <v>22.05915178571428</v>
+      </c>
+      <c r="O18" t="n">
+        <v>18.13988095238095</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.263392857142857</v>
+      </c>
+      <c r="X18" t="n">
+        <v>6.432291666666666</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.307849702380952</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.962053571428571</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.473338293650793</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +2066,79 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>11.45508625817966</v>
+        <v>4366.439909297052</v>
       </c>
       <c r="D19" t="n">
-        <v>24.79445645285816</v>
+        <v>484.0822450319926</v>
       </c>
       <c r="E19" t="n">
-        <v>14.42956731377578</v>
+        <v>281.7201237451462</v>
       </c>
       <c r="F19" t="n">
         <v>1.718309074256655</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2341526319218664</v>
+        <v>0.2341526319218663</v>
       </c>
       <c r="H19" t="n">
+        <v>16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.363467261904762</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.82068452380952</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.301316034226189</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>1.204077743902439</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.732278963414634</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.468178353658537</v>
+      <c r="M19" t="n">
+        <v>33.82068452380952</v>
+      </c>
+      <c r="N19" t="n">
+        <v>23.50818452380952</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7.475818452380952</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.849808673469387</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.363467261904762</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>4.042038690476191</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.649075255102041</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>12.23586309523809</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2149,79 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11.23735871505056</v>
+        <v>4283.446712018141</v>
       </c>
       <c r="D20" t="n">
-        <v>26.68709011194183</v>
+        <v>521.0336640902927</v>
       </c>
       <c r="E20" t="n">
-        <v>14.15607455590876</v>
+        <v>276.3805032344092</v>
       </c>
       <c r="F20" t="n">
         <v>1.885204122551234</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1982766918745933</v>
+        <v>0.1982766918745934</v>
       </c>
       <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.636904761904762</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.78050595238095</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8.540798611111112</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>1.258003048780488</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.781440548780488</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.519721798780488</v>
+      <c r="M20" t="n">
+        <v>34.78050595238095</v>
+      </c>
+      <c r="N20" t="n">
+        <v>24.56101190476191</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4.694940476190476</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8.681175595238095</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.673280423280421</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.636904761904762</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>3.151041666666667</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.177734375</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>8.678075396825397</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2232,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10.99077929803688</v>
+        <v>4189.455782312925</v>
       </c>
       <c r="D21" t="n">
-        <v>26.68954144454584</v>
+        <v>521.0815234411331</v>
       </c>
       <c r="E21" t="n">
-        <v>14.03830802149889</v>
+        <v>274.0812518483116</v>
       </c>
       <c r="F21" t="n">
-        <v>1.901193605644803</v>
+        <v>1.901193605644804</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1938903196675855</v>
+        <v>0.1938903196675854</v>
       </c>
       <c r="H21" t="n">
+        <v>17</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.061011904761905</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.69568452380952</v>
+      </c>
+      <c r="K21" t="n">
+        <v>8.239999124649856</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>1.374333079268293</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.828315548780488</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.60132431402439</v>
+      <c r="M21" t="n">
+        <v>35.69568452380952</v>
+      </c>
+      <c r="N21" t="n">
+        <v>26.83221726190476</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5.100446428571428</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9.047619047619047</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.562313988095238</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.061011904761905</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.974330357142857</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.385788690476191</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>5.798611111111111</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2314,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>5.118719362745098</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2336,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>10.24859943977591</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2353,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>7.165165111183362</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>3.889508928571428</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.989211309523809</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>3.597470238095238</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>1.639281580687831</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.868737599206349</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.687051537435962</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/35/Filled_2D_sections/axial/week35_axial_Batch_Allmarks.xlsx
+++ b/measurements/35/Filled_2D_sections/axial/week35_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2472,4 +2678,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week35_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4460.102040816326</v>
+      </c>
+      <c r="D10" t="n">
+        <v>104.2328107958234</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4189.455782312925</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4610.31746031746</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>575.8206181043671</v>
+      </c>
+      <c r="D11" t="n">
+        <v>44.10015383436588</v>
+      </c>
+      <c r="E11" t="n">
+        <v>484.0822450319926</v>
+      </c>
+      <c r="F11" t="n">
+        <v>655.4383214882441</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.934763146939909</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1145491496381267</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.718309074256655</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.14201256102238</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1716428418731661</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.02501465160929707</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1291305357244266</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2341526319218663</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0140.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0142.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>17</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>16</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>15</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>15</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>16</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>9</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>9</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>17</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>17</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.980829172474577</v>
+      </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.6155870112510924</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.88832981062213</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.744163198544762</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>56</v>
+      </c>
+      <c r="C48" t="n">
+        <v>24.68049133715986</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.908084684833144</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.67559523809524</v>
+      </c>
+      <c r="F48" t="n">
+        <v>40.33854166666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>105</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.213453089569161</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.197109040789527</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.263392857142857</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13.27938988095238</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>122</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.759334138368462</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7792412592921759</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.363467261904762</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.47172619047619</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>